--- a/Data/BugTracker/BugTracker.xlsx
+++ b/Data/BugTracker/BugTracker.xlsx
@@ -145,7 +145,7 @@
     <x:t>WWWWWWWWWWWWWWWWWWWWWWWW</x:t>
   </x:si>
   <x:si>
-    <x:t>Ready To Vet</x:t>
+    <x:t>Approved</x:t>
   </x:si>
   <x:si>
     <x:t>ghjgjghjgj</x:t>
@@ -154,6 +154,9 @@
     <x:t>fggffgfgf</x:t>
   </x:si>
   <x:si>
+    <x:t>Yes</x:t>
+  </x:si>
+  <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
@@ -163,10 +166,10 @@
     <x:t>WWWWWWW</x:t>
   </x:si>
   <x:si>
-    <x:t>Approved</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Yes</x:t>
+    <x:t>Bimbo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bombo</x:t>
   </x:si>
   <x:si>
     <x:t>5</x:t>
@@ -175,7 +178,7 @@
     <x:t>Inconsistent Translation</x:t>
   </x:si>
   <x:si>
-    <x:t>[FR, DE, ES]</x:t>
+    <x:t>[FR, ES]</x:t>
   </x:si>
   <x:si>
     <x:t>Reporting</x:t>
@@ -187,7 +190,7 @@
     <x:t>Shortening</x:t>
   </x:si>
   <x:si>
-    <x:t>zdhhdhdh</x:t>
+    <x:t>[DE] gsgdfgdfgdf</x:t>
   </x:si>
   <x:si>
     <x:t>fjfgjgjsgj</x:t>
@@ -223,13 +226,28 @@
     <x:t>FFFFFF</x:t>
   </x:si>
   <x:si>
+    <x:t>Not a bug</x:t>
+  </x:si>
+  <x:si>
     <x:t>9</x:t>
   </x:si>
   <x:si>
-    <x:t>[IT, DE, ES] ggggg</x:t>
+    <x:t>[DE, ES] ggggg</x:t>
   </x:si>
   <x:si>
     <x:t>gdgdhfhdh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026/10/15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Incorrect Translation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[DE]</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -580,10 +598,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:W10"/>
+  <x:dimension ref="A1:W11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="1.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="2.996339" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="9.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="10.996339" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="22.710625" style="0" customWidth="1"/>
@@ -591,7 +609,7 @@
     <x:col min="6" max="6" width="45.996339" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="49.996339" style="0" customWidth="1"/>
     <x:col min="8" max="11" width="11.853482" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.424911" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="22.424911" style="0" customWidth="1"/>
     <x:col min="14" max="15" width="21.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="20.996339" style="0" customWidth="1"/>
@@ -885,12 +903,12 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="W4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>24</x:v>
@@ -902,10 +920,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>33</x:v>
@@ -923,7 +941,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
         <x:v>33</x:v>
@@ -932,10 +950,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="P5" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q5" s="0" t="s">
         <x:v>33</x:v>
@@ -956,12 +974,12 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="W5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>24</x:v>
@@ -970,10 +988,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>33</x:v>
@@ -988,13 +1006,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
         <x:v>33</x:v>
@@ -1032,7 +1050,7 @@
     </x:row>
     <x:row r="7" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>24</x:v>
@@ -1041,16 +1059,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>29</x:v>
@@ -1103,7 +1121,7 @@
     </x:row>
     <x:row r="8" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A8" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>24</x:v>
@@ -1112,16 +1130,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>29</x:v>
@@ -1136,7 +1154,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
         <x:v>33</x:v>
@@ -1174,25 +1192,25 @@
     </x:row>
     <x:row r="9" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A9" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>30</x:v>
@@ -1207,7 +1225,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
         <x:v>33</x:v>
@@ -1245,31 +1263,31 @@
     </x:row>
     <x:row r="10" spans="1:23" ht="14.25" customHeight="1">
       <x:c r="A10" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
         <x:v>30</x:v>
@@ -1311,6 +1329,77 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="W10" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:23" ht="14.25" customHeight="1">
+      <x:c r="A11" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="Q11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="R11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="T11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="U11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="V11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="W11" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
